--- a/Day 03 - Git GitHub Test Documentation/test-plans/Test_Plan.xlsx
+++ b/Day 03 - Git GitHub Test Documentation/test-plans/Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eaebac77f309a14c/Desktop/Linkific-Tasks-main/Day 03 - Git GitHub Test Documentation/test-plans/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_A84FA29F115B888E6E5B88B74B621E7CF7A8ACFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64D72AE9-D350-4007-ADE5-CE6079482044}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_A84FA29F115B888E6E5B88B74B621E7CF7A8ACFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBE16DA3-FB51-4D4A-96E4-D4CD67E10BA8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,10 +52,10 @@
     <t>Exit Criteria</t>
   </si>
   <si>
-    <t>Risks</t>
-  </si>
-  <si>
     <t>Test Deliverables</t>
+  </si>
+  <si>
+    <t>Risks and Mitigation</t>
   </si>
 </sst>
 </file>
@@ -134,6 +134,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -461,10 +465,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
